--- a/光伏配储项目/电价数据/2026/雁山站.xlsx
+++ b/光伏配储项目/电价数据/2026/雁山站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51758</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.95684</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.59939</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.78084</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.6440499999999999</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.61482</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43781</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45434</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44053</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42286</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42904</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40844</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39752</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39921</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3839</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40173</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42293</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41157</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39099</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38446</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41597</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39255</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42199</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42293</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41252</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44397</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.39015</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30403</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26277</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.30253</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.5124099999999999</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.44916</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.2671</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.17697</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.23906</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.2823</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.1062</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.20397</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.41727</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.20129</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.01248</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.25956</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.09619</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.19313</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.24792</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.27283</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.25353</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.4814</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.08181999999999999</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.17587</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.40586</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.41857</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.50346</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.44894</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.42939</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.59954</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.08678</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.17231</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.13734</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.51045</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.89899</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.6595800000000001</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.54644</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6357699999999999</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.76698</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.6962200000000001</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.99642</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.14199</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.85249</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.8804099999999999</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.24341</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.6472100000000001</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.9322999999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.78225</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.60711</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.9085800000000001</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.8268</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.8660599999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.83894</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.58192</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47944</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40189</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41307</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42232</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.8703500000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8444400000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.88314</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53607</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5225</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5062300000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.53728</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.4119</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47258</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38931</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37073</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37548</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37545</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42121</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.52161</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.65847</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.72409</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.44167</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.38341</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.44766</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.6088899999999999</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.6997000000000001</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.44301</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.54437</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.47106</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.39201</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.39749</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.47066</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.69136</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.7270800000000001</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.01554</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.65032</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.71914</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.58815</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.62294</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.98368</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.73924</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.50689</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.62421</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29496</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.46679</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.36636</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.36888</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.81763</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.5913200000000001</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.5224500000000001</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.57926</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.57999</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.40375</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.42589</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.70812</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.58169</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.52671</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.74129</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.53174</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.00454</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.16941</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.08704</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.92703</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.02491</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.00853</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.16922</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.8389099999999999</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.91555</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.16355</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.5861000000000001</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.38225</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.50842</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.50182</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.6618999999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44074</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43475</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41808</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33353</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5156000000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.39909</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.50522</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.3986</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40609</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39561</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38255</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43385</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39346</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36631</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47351</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45008</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44425</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36835</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.48483</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.4186</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.45735</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.40848</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.37256</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.46054</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30276</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.35314</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.5764</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.57533</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.81037</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.45056</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.6791799999999999</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.78288</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.43866</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.43182</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.48402</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.52288</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.5904700000000001</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.56484</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.42237</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.33762</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.5801900000000001</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.5829500000000001</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.6081799999999999</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.80249</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.21158</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.68512</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.80628</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.21133</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.62478</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.56957</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.49233</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.6126200000000001</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.88798</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.86136</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.7993300000000001</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.56421</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.78432</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.7095199999999999</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.97141</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6397</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.91089</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.63287</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.65374</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.6397999999999999</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.6612</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.5951900000000001</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.6842</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.61386</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.51595</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.5199600000000001</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.42706</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34312</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.61068</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49421</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.4045299999999999</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.42911</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.41412</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.39336</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46675</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30171</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.3578</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38916</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.36445</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43055</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.38201</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.52511</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.5019100000000001</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.39343</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.44358</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.52403</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.45463</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.8109500000000001</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.72541</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.50762</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.63062</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.5737100000000001</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.41147</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.29401</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.27113</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.48687</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.7025800000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.49017</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.46884</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.47517</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.43912</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.4586</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.42522</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.76237</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.44501</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.92932</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.43654</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.44006</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.48207</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.44567</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.49061</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.5650599999999999</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.55537</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.60925</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.58086</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.83114</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.56333</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.53451</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.46879</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.48559</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.5021100000000001</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.50659</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.47716</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.4661</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.3973</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.40179</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.30143</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30866</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.30077</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37269</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.40513</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38786</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29383</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30699</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29323</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29641</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29658</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29838</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30695</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.28797</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.27282</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.11832</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.11914</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.12116</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.09284999999999999</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.08841</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.10011</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.09099</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.1111</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.01982</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.02538</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.02946</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.07312</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.09358</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.05778</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.07106999999999999</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.01519</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.07546</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.01379</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.09111</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.07027</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.01435</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.0479</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.04695000000000001</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.04347</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.05268</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.03139</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21026</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.09093999999999999</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.09181</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.09503</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.00731</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.05191</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.01065</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.21553</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.1174</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.17335</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.35292</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39319</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.40319</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37514</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39955</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39843</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40989</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.46277</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.37752</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.76601</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.5015500000000001</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.54277</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.45322</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.44858</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36656</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.36887</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.36531</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.36458</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30597</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.13558</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04874</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04658</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.01212</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04524</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04481</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04168</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.02868</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.13146</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.01249</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04336</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.01498</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04282</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.0449</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04479</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04485</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.03524</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04229</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04457</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04208</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04231</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.01215</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04447</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04476</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04247</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.01345</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.01187</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04988</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.01372</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.01242</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.01385</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.01692</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.23074</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.19007</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.30758</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.28734</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35332</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36599</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33621</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.33792</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40554</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28766</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29449</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.29314</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28723</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.2783</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28621</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.19494</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.18304</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1718</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15938</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23744</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2148</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.23962</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27541</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.29024</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29531</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.2961</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28755</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28818</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28782</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27788</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28833</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.39446</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.46022</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.38595</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.43964</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.45274</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.5256900000000001</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45746</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.42763</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.47352</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.45606</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.49453</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15306</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29307</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.41449</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.38377</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.39075</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.42695</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47944</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.55055</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7925800000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.65324</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.43894</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.54531</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.82745</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.01472</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.56224</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.02005</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.98477</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.40694</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.45365</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.9980599999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.71338</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.32083</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.9778300000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.8720800000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.43011</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.12298</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5929800000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.80541</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303600000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78777</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78904</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87859</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88144</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5067</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41216</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41733</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46543</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.22444</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63947</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54264</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50258</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45789</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42623</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.4401600000000001</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45067</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39254</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45282</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42071</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39061</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40651</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45089</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39743</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40012</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5895</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42944</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59624</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5965499999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66151</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.5512100000000001</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.45387</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5652699999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.47245</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.9763099999999999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.69768</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.92475</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.90586</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.91735</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.36887</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.44347</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.50526</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.48013</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.42543</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.60493</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.39157</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.39506</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.36368</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.40128</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.37399</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.38198</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.37253</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.37093</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.36896</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.37726</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.40456</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.38432</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.38404</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.40837</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.39293</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.38869</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.38416</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.36722</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.42566</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41256</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.4523</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41492</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39144</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37489</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35326</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95636</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47698</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40788</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.48241</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.54504</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39258</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40967</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.39186</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.41429</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.38371</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38536</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40007</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50008</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.40227</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.37532</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.41399</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.44833</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.39085</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.23557</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.42503</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.40935</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.4463</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.40951</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.37618</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.39558</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.40817</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.23092</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.28234</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.29544</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.42339</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.55376</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.45579</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.39069</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.48208</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.40981</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.40281</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.37165</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.53003</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.38844</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.27003</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.29536</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.27824</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.22685</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.29484</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>-0.02403</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43249</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.29429</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40172</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40045</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59676</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.93992</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.45005</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.20179</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70362</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79538</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64981</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58368</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42355</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.56714</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.42734</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.70272</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.50831</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.45881</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.5382899999999999</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.54331</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.8498</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.70124</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.59862</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.44642</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.75954</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.7575700000000001</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.45884</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.45624</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.44473</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.65076</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.6897000000000001</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.50542</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.47974</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.47164</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.42978</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.42101</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.41602</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.41966</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.47642</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.46749</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.44091</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.48724</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.59615</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.50861</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.47058</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.50506</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.45493</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.45788</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.57324</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.50088</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.47609</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.5152100000000001</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.46396</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.4516</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.7821</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.58221</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.93467</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.6770499999999999</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.53838</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.49522</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.4837</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38651</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32473</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42553</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39151</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.30907</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.01727</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.26721</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.18479</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.18915</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.2006</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.58463</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.5906699999999999</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.17442</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.18057</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.19795</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.19454</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.29846</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.20447</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.19137</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.18259</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.1746</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.17795</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.2054</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.20116</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.18636</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.4096</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.37514</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.4052</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44972</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.3998</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40189</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39773</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44368</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43993</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43929</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44421</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44428</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40266</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39053</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39771</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54243</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38908</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46869</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42387</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41594</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39307</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38023</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39107</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37558</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28935</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31353</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28651</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28617</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26196</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.26867</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.25807</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.22776</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.24712</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29822</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28976</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.29157</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29395</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30347</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28588</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.26432</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30993</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31393</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.36642</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.44463</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.41821</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.41125</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.46696</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.57659</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.55379</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.47621</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.37855</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.37971</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.45806</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.51387</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.57766</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.58073</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.45093</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.40676</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3972</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.37543</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.4195</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39258</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.38972</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.39163</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.38317</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36026</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41861</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.39479</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.46116</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.53483</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.5414</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.53012</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.53252</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.72074</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.70861</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.48242</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.5873700000000001</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.8356399999999999</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.51427</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.81985</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.6998300000000001</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.6925399999999999</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.7599600000000001</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.21121</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.56445</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27443</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.80725</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.28436</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.5329299999999999</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.55762</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.52337</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.69213</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.67522</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.7086</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.72194</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.7170700000000001</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.69423</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.7186900000000001</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.59604</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.7518400000000001</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.86622</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.83316</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.81038</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.74875</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.75648</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.7645599999999999</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.7123400000000001</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.79884</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.5220199999999999</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.55814</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.7425700000000001</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.75093</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.74485</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.96851</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.82425</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.14093</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.7744500000000001</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.86961</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.49141</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.4469</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.15181</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.7872</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.55137</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.38013</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31159</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.39353</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.56374</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33358</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33872</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.57426</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.57874</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.45496</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.37115</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.38312</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.38064</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.28952</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29849</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2817</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31391</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.34334</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.38168</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.49949</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.65662</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.5876699999999999</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.51262</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.45679</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.37377</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.38297</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.41223</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39285</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40286</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36941</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34931</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29295</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.45519</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.38484</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.75682</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.38142</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.37878</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5624</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.37756</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.39471</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.37315</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.47187</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.40226</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.40388</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42965</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40916</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38572</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38502</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65197</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83087</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47176</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40089</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45943</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34477</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41077</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37582</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.28972</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.20909</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.4015</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.29539</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.29423</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.22575</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.3419700000000001</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28845</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.02343</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.24879</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29902</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.21971</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.0395</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.19195</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.06759</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.28406</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.46456</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.54908</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.57168</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.45228</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.50319</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.52476</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.00091</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.49901</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.9798300000000001</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.37885</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.32875</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.67206</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>1.44651</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.52135</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>1.03376</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.58318</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.48811</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>1.04669</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.9358500000000001</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.5761000000000001</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.6289</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.62551</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43003</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41894</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37447</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36015</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.5499700000000001</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.7722100000000001</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.6785800000000001</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.95786</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41942</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40556</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40492</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41134</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40902</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41774</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39586</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41163</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40937</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.3871</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41848</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38725</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41662</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39007</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41248</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45051</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44949</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56059</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5006499999999999</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.42028</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.81136</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.83163</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.11225</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.17979</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.29944</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.40574</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.31931</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.18435</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.72496</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.74842</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.8449099999999999</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.56992</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.56008</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.57468</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>-0.03927000000000001</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>-0.04167</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.24459</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.99485</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.73876</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.4808</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.07606</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.62683</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.56655</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.48056</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.63203</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.47576</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.60387</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.3742799999999999</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.41721</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.40823</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.4758</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.56455</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.45681</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.5331399999999999</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.44386</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.54767</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.58772</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.7656799999999999</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.7146699999999999</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.65652</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.65766</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.64986</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.77739</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.03582</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.53404</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.16691</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.08152</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.82586</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8487</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.78426</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.63546</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.06017</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.6642</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.74736</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.60482</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47839</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47173</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.4194</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5483</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.39639</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45813</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43679</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42655</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44836</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41783</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.4577</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39934</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38854</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38657</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.40539</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39151</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.44125</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39447</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.38522</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.43861</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.4287</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.44293</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.47754</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.5964700000000001</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.7223099999999999</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.10016</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.14674</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.15745</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.01254</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.36779</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.40888</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.4053</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.41971</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.4367200000000001</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.42159</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36371</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41731</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.44987</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.43083</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.45657</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38628</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40611</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40201</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39922</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36415</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.51306</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.52818</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.46392</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.43042</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.38862</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37714</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.37423</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.36709</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.25656</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.27442</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.25085</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.26706</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.04733</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.19889</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29668</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29826</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.08162</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.18465</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.27974</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.03716</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.18251</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.19332</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.06968000000000001</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.02976</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24322</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25083</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.17662</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23508</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.28006</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27127</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.3714</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.42726</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.39491</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.41318</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.39811</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.41666</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.37068</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.42589</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39575</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.38889</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.39244</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.41545</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36616</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.3517</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.41837</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30616</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29716</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.26173</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.25576</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.17079</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.21055</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.44959</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.09769</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.08383</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.04345</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.03119</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.19245</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.04256</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.04259</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.02905</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.11799</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.20447</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.12862</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.05697</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.04448</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.04209</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.11631</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.02712</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.03459</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.02979</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.02727</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.03727</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.10382</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.06872</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.02688</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.02989</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.0269</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.02699</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.03915</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.03033</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.06869</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.04743</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.17509</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.21084</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.25569</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.29498</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.27685</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.28166</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.27378</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.27892</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29173</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.29599</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29964</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28743</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30605</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29582</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29973</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.46524</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.28271</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29038</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.27831</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.26947</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.23099</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.13957</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.54845</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.17495</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28467</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.26483</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.29384</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.28149</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.26272</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.24553</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.23357</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.25056</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.25663</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.22257</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.25957</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.24884</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.26278</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.27142</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.27259</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.25015</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.2894</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.26559</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41268</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27688</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.22774</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.15474</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.62798</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.63098</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.74252</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.58897</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.48849</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.16987</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.27517</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.15553</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.12945</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>1.15061</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.17006</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28512</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.15666</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.12411</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.00446</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.13907</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.19506</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.06606000000000001</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.20582</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.04149</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.14908</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.25013</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.10008</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.19458</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.5419299999999999</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.18232</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.41202</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.39853</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.5397999999999999</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.48907</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.50497</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.50578</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.50556</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.5510499999999999</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.42364</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.52652</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.4392</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.54969</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.98123</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.7110599999999999</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.69659</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.73238</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.8677699999999999</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.71151</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.74265</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.75735</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.86746</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.5718099999999999</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.51918</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.56143</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.56026</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.6791699999999999</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.5835</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.48842</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.42268</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32942</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.46385</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.38725</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.42918</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.42924</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.38146</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.14726</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.9559500000000001</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.75919</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.6628200000000001</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.61287</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.4935</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.57996</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.49993</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.44072</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.09642</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.6349900000000001</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.54748</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.6379600000000001</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.72249</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.71709</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.55862</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.5764</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.4565</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.4172</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.1655</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.37142</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.28704</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.23231</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.39413</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.5930700000000001</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.17657</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.36205</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.37206</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.39345</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.39838</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.38962</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.39637</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.37264</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.38884</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40714</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.39887</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.43433</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.5644600000000001</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.5574</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.4357</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.37315</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.77363</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.50097</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.49294</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.5717000000000001</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.53803</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.41248</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.41422</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.40275</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.38392</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.39188</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33369</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.36678</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31318</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36911</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37351</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.43238</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.55491</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.44114</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.55702</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.79077</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.7258600000000001</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.95202</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.05813</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.40213</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.5142100000000001</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.55077</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.49697</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.47054</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.50429</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.48319</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.4719100000000001</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.38075</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.47508</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.65147</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.46629</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.49371</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.49278</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.12962</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.47461</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.42324</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.48592</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.5089</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.5039399999999999</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.55137</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.66449</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.6870700000000001</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.73397</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.80052</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.7837000000000001</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.8537100000000001</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.86619</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.84393</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.71158</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.61486</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.59768</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.47274</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.7197100000000001</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.55149</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.62539</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.54964</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.5784</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.5547300000000001</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.52062</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.5412100000000001</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42415</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.68368</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.50464</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40151</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45846</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.46495</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.51002</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.48136</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36868</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.56809</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40124</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37729</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37575</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.37665</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.39379</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.46909</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.39079</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.6086</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.59792</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.5892200000000001</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.65452</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.6626299999999999</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.56797</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.75039</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.81609</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.53096</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.45835</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.53911</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.52185</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.52197</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.24029</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.23198</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.2507</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.49893</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.45891</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.43579</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.20436</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.48417</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.55768</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.5405599999999999</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.43418</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.62999</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.6323200000000001</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.41885</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.65325</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.42243</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.40406</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.75854</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.6157100000000001</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.59645</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.46496</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.53847</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.49774</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.49829</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.32066</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45687</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.54755</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.5314</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.25835</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.68841</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.46776</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.44604</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.27067</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.72263</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.48949</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.49127</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.50673</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.48512</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.44905</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37505</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27078</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.41533</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.38782</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29638</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.28934</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.36436</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.45858</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.41336</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.36953</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.5839299999999999</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.49187</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.77638</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.27381</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.2015</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.14691</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.77208</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.6743300000000001</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.2062</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.09658</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.00013</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.11254</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.10005</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.24361</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.01304</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.22412</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.09656999999999999</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.2289</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.21454</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.14492</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.25191</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.51824</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.5139</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.39656</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.37223</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.46315</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.53984</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.59197</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.46539</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.47812</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.39131</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.4596</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.47019</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.13641</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>-0.009859999999999999</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.25252</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.27156</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.52891</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.50927</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.51527</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.54522</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.53074</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.51251</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.6418200000000001</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.48581</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.50395</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.45431</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.43995</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.38641</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37531</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.01243</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.52206</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.57577</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.6336799999999999</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.4773</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36316</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38825</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36605</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38018</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36397</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36594</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38323</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.42031</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.42363</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.40944</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.41339</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.4189</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.5591900000000001</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.30198</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.24678</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.4455</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.27821</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.08846</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.07386</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.13548</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.08751</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.17356</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.48789</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.23116</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.2946</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.2002</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1.12962</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.89155</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.83551</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.43104</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.7328</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.10062</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.17928</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.8382500000000001</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.5774199999999999</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.5039399999999999</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.77678</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.78925</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.54208</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.76876</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.5608099999999999</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.59417</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.5855399999999999</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.57197</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.78616</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.6382599999999999</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.64164</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.65199</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.77778</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.5388999999999999</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.56209</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.51066</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.58328</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.7072999999999999</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.76378</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.55925</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.4353</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.40998</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.40585</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.6753400000000001</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.44151</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.44442</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.38981</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.38426</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.38237</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41964</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.38999</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37333</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.36312</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28061</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.25723</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.23957</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.16994</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.22306</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.30751</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.27013</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.25228</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.36873</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.31155</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.23746</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.19291</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.23379</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.22917</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.2118</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.14149</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.15303</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.20087</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.15101</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.19806</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.16115</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.27086</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.22999</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.18063</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.11853</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19841</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.22007</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.2778</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.21359</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.48858</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.38851</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.38651</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.38994</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.40184</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.44837</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.47196</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.42307</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.43649</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.5210399999999999</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.46758</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.45364</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.42925</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.43792</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.54226</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.56211</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.51288</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.44442</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.44972</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.42391</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.4053</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40849</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40967</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38407</v>
       </c>
     </row>
   </sheetData>
